--- a/NECP Scenario/Results/Regional Results/LEMNOS_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/LEMNOS_Capacity.xlsx
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.236210025195272E-08</v>
+        <v>4.777648045028226E-08</v>
       </c>
       <c r="C3">
-        <v>3.251979805748589E-08</v>
+        <v>4.800846450710878E-08</v>
       </c>
       <c r="D3">
-        <v>0.011230051151431</v>
+        <v>0.0112300163058436</v>
       </c>
       <c r="E3">
-        <v>0.356984663380908</v>
+        <v>0.4041212269445549</v>
       </c>
       <c r="F3">
-        <v>0.4262799784679034</v>
+        <v>0.5024271600682748</v>
       </c>
       <c r="G3">
-        <v>0.4730937794466442</v>
+        <v>0.5323160530700003</v>
       </c>
       <c r="H3">
-        <v>0.4688986438478594</v>
+        <v>0.5271962002164148</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.4000000000065395</v>
+        <v>0.4000000000070728</v>
       </c>
       <c r="C13">
-        <v>0.4000000000085822</v>
+        <v>0.4000000000100733</v>
       </c>
       <c r="D13">
-        <v>0.4000000000127875</v>
+        <v>0.4000000000157209</v>
       </c>
       <c r="E13">
-        <v>0.4000000000234579</v>
+        <v>0.4000000000288511</v>
       </c>
       <c r="F13">
-        <v>0.4000000000404795</v>
+        <v>0.4000000000495168</v>
       </c>
       <c r="G13">
-        <v>0.4000000000745622</v>
+        <v>0.4000000000944524</v>
       </c>
       <c r="H13">
-        <v>0.4000000004252446</v>
+        <v>0.4000000005044353</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1163,19 +1163,19 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0.0326941860443778</v>
+        <v>0.032694089229652</v>
       </c>
       <c r="E27">
-        <v>0.1240105891575719</v>
+        <v>0.1312849921469748</v>
       </c>
       <c r="F27">
-        <v>0.1338100493127074</v>
+        <v>0.1338100491004125</v>
       </c>
       <c r="G27">
-        <v>0.1338100496857623</v>
+        <v>0.1338100495760603</v>
       </c>
       <c r="H27">
-        <v>0.1338100498582055</v>
+        <v>0.1338100498092189</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1215,19 +1215,19 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>3.676412498675807E-08</v>
+        <v>5.43384748409135E-08</v>
       </c>
       <c r="E29">
-        <v>0.0113537963049231</v>
+        <v>0.01149800049396</v>
       </c>
       <c r="F29">
-        <v>0.0150947071540093</v>
+        <v>0.0163667727071575</v>
       </c>
       <c r="G29">
-        <v>0.0163667794992789</v>
+        <v>0.0163667794719381</v>
       </c>
       <c r="H29">
-        <v>0.0163667798077312</v>
+        <v>0.0163667797886908</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1319,19 +1319,19 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0.0075296986074557</v>
+        <v>0.0075297064568431</v>
       </c>
       <c r="E33">
-        <v>0.3962249582875963</v>
+        <v>0.3814980886735321</v>
       </c>
       <c r="F33">
-        <v>0.4479208977748406</v>
+        <v>0.4478630545575696</v>
       </c>
       <c r="G33">
-        <v>0.4479208998934419</v>
+        <v>0.447863056273664</v>
       </c>
       <c r="H33">
-        <v>0.447920901476566</v>
+        <v>0.4478630583563395</v>
       </c>
     </row>
     <row r="34" spans="1:8">
